--- a/output/2026-10-05_03_Malesia_Terengganu_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-05_03_Malesia_Terengganu_Impiantistica_aspirazione_industriale.xlsx
@@ -489,11 +489,9 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda 100% Bumiputera con sede a Kemaman, Terengganu, specializzata in Industrial Hygiene e Local Exhaust Ventilation (LEV). Fornisce design, fornitura, fabbricazione, installazione, manutenzione e training per sistemi LEV/HVAC/APCS per conto terzi (fornitore B2B, non cliente finale). Fonti: sme100.asia, village.ai/company/zabsi, sgpgrid.com.</t>
+          <t>Azienda 100% Bumiputera con sede a Kemaman, Terengganu, specializzata in Industrial Hygiene e Local Exhaust Ventilation (LEV). Fornisce design, fornitura, fabbricazione, installazione, manutenzione e training per sistemi LEV/HVAC/APCS per conto terzi (fornitore B2B, non cliente finale). Fonti: sme100.asia, village.ai/company/zabsi, sgpgrid.com. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
